--- a/artfynd/A 45233-2021 artfynd.xlsx
+++ b/artfynd/A 45233-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 45233-2021 artfynd.xlsx
+++ b/artfynd/A 45233-2021 artfynd.xlsx
@@ -675,53 +675,57 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>95683329</v>
+        <v>95999523</v>
       </c>
       <c r="B2" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>N Rågrecken, Vstm</t>
+          <t>Norr Rågrecken, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>489025.7459798299</v>
+        <v>489080</v>
       </c>
       <c r="R2" t="n">
-        <v>6608258.856672035</v>
+        <v>6608342</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-08-23</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-08-23</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-07</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,31 +765,31 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Emil Pagstedt Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Emil Pagstedt Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>95683212</v>
+        <v>95683329</v>
       </c>
       <c r="B3" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>489023.2173682185</v>
+        <v>489026</v>
       </c>
       <c r="R3" t="n">
-        <v>6608260.888234628</v>
+        <v>6608259</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -860,19 +854,9 @@
           <t>2021-08-23</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-08-23</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,16 +886,11 @@
         <v>95683330</v>
       </c>
       <c r="B4" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -939,10 +918,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>489041.1056190809</v>
+        <v>489041</v>
       </c>
       <c r="R4" t="n">
-        <v>6608310.93344841</v>
+        <v>6608311</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -972,19 +951,9 @@
           <t>2021-08-23</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-08-23</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,15 +980,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>95999523</v>
+        <v>95999521</v>
       </c>
       <c r="B5" t="n">
-        <v>90669</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,21 +991,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1060,10 +1024,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>489079.7215008711</v>
+        <v>489045</v>
       </c>
       <c r="R5" t="n">
-        <v>6608342.194624076</v>
+        <v>6608360</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,19 +1057,9 @@
           <t>2021-09-07</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2021-09-07</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1140,16 +1094,11 @@
         <v>95999522</v>
       </c>
       <c r="B6" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1186,10 +1135,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>489039.1534896225</v>
+        <v>489039</v>
       </c>
       <c r="R6" t="n">
-        <v>6608336.746730641</v>
+        <v>6608337</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1219,19 +1168,9 @@
           <t>2021-09-07</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2021-09-07</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1263,19 +1202,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>95999525</v>
+        <v>95999524</v>
       </c>
       <c r="B7" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1312,10 +1246,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>489129.7648456986</v>
+        <v>489097</v>
       </c>
       <c r="R7" t="n">
-        <v>6608293.976148552</v>
+        <v>6608329</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1345,19 +1279,9 @@
           <t>2021-09-07</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2021-09-07</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1389,19 +1313,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>95999521</v>
+        <v>95999525</v>
       </c>
       <c r="B8" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1438,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>489044.7974008588</v>
+        <v>489130</v>
       </c>
       <c r="R8" t="n">
-        <v>6608360.007496554</v>
+        <v>6608294</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1471,19 +1390,9 @@
           <t>2021-09-07</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2021-09-07</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1515,62 +1424,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>95999524</v>
+        <v>95683212</v>
       </c>
       <c r="B9" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Norr Rågrecken, Vstm</t>
+          <t>N Rågrecken, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>489096.9162413118</v>
+        <v>489023</v>
       </c>
       <c r="R9" t="n">
-        <v>6608328.481773067</v>
+        <v>6608261</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1594,22 +1489,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2021-09-07</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-23</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2021-09-07</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-23</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1620,21 +1505,16 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Emil Pagstedt Andersson</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Emil Pagstedt Andersson</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 45233-2021 artfynd.xlsx
+++ b/artfynd/A 45233-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95999523</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -880,6 +890,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95683329</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -977,6 +992,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95683330</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1088,6 +1108,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95999521</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1199,6 +1224,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95999522</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1310,6 +1340,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95999524</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1421,6 +1456,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95999525</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1518,8 +1558,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95683212</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>